--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9489,0.0015,0.0114,0.0088</t>
-  </si>
-  <si>
-    <t>0.9664,0.0009,0.0015,0.0175</t>
-  </si>
-  <si>
-    <t>0.9564,0.0009,0.0026,0.0251</t>
-  </si>
-  <si>
-    <t>0.9819,0.0002,0.0004,0.0148</t>
-  </si>
-  <si>
-    <t>0.9363,0.0043,0.0029,0.0260</t>
-  </si>
-  <si>
-    <t>0.9419,0.0015,0.0005,0.0525</t>
-  </si>
-  <si>
-    <t>0.8435,0.0054,0.0165,0.1560</t>
-  </si>
-  <si>
-    <t>0.9076,0.0008,0.0009,0.1081</t>
-  </si>
-  <si>
-    <t>0.8641,0.0047,0.0053,0.1164</t>
-  </si>
-  <si>
-    <t>0.7928,0.0038,0.0015,0.1602</t>
-  </si>
-  <si>
-    <t>0.8711,0.0046,0.0177,0.0529</t>
-  </si>
-  <si>
-    <t>0.9711,0.0017,0.0014,0.0160</t>
-  </si>
-  <si>
-    <t>0.9635,0.0019,0.0262,0.0005</t>
-  </si>
-  <si>
-    <t>0.9530,0.0012,0.0511,0.0009</t>
-  </si>
-  <si>
-    <t>0.8273,0.0143,0.2478,0.0013</t>
-  </si>
-  <si>
-    <t>0.9668,0.0014,0.0294,0.0003</t>
-  </si>
-  <si>
-    <t>0.9576,0.0035,0.0303,0.0005</t>
-  </si>
-  <si>
-    <t>0.9699,0.0062,0.0089,0.0005</t>
-  </si>
-  <si>
-    <t>0.9476,0.0133,0.0178,0.0018</t>
-  </si>
-  <si>
-    <t>0.9322,0.0209,0.0116,0.0044</t>
-  </si>
-  <si>
-    <t>0.8844,0.0378,0.0238,0.0013</t>
-  </si>
-  <si>
-    <t>0.9768,0.0098,0.0024,0.0007</t>
-  </si>
-  <si>
-    <t>0.9644,0.0006,0.0382,0.0003</t>
-  </si>
-  <si>
-    <t>0.9883,0.0002,0.0036,0.0006</t>
-  </si>
-  <si>
-    <t>0.7302,0.0004,0.4990,0.0001</t>
-  </si>
-  <si>
-    <t>0.9819,0.0004,0.0097,0.0005</t>
-  </si>
-  <si>
-    <t>0.7452,0.0040,0.4779,0.0009</t>
-  </si>
-  <si>
-    <t>0.8021,0.0008,0.2149,0.0017</t>
-  </si>
-  <si>
-    <t>0.0098,0.0059,0.9900,0.0024</t>
-  </si>
-  <si>
-    <t>0.9916,0.0005,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.9506,0.0120,0.0222,0.0024</t>
-  </si>
-  <si>
-    <t>0.0226,0.0610,0.9692,0.0049</t>
-  </si>
-  <si>
-    <t>0.8946,0.0919,0.0070,0.0002</t>
-  </si>
-  <si>
-    <t>0.9758,0.0007,0.0078,0.0020</t>
-  </si>
-  <si>
-    <t>0.9619,0.0033,0.0079,0.0055</t>
-  </si>
-  <si>
-    <t>0.9438,0.0004,0.0081,0.0117</t>
-  </si>
-  <si>
-    <t>0.9304,0.0112,0.0269,0.0071</t>
-  </si>
-  <si>
-    <t>0.4540,0.2699,0.1301,0.0021</t>
-  </si>
-  <si>
-    <t>0.3685,0.0008,0.8983,0.0001</t>
-  </si>
-  <si>
-    <t>0.8387,0.0007,0.3401,0.0002</t>
-  </si>
-  <si>
-    <t>0.9549,0.0008,0.0499,0.0005</t>
-  </si>
-  <si>
-    <t>0.9394,0.0019,0.1018,0.0002</t>
-  </si>
-  <si>
-    <t>0.3116,0.3475,0.2626,0.0014</t>
-  </si>
-  <si>
-    <t>0.1654,0.0325,0.9211,0.0011</t>
-  </si>
-  <si>
-    <t>0.9848,0.0021,0.0026,0.0011</t>
-  </si>
-  <si>
-    <t>0.9094,0.0177,0.0271,0.0036</t>
-  </si>
-  <si>
-    <t>0.8154,0.1465,0.0114,0.0006</t>
-  </si>
-  <si>
-    <t>0.8835,0.0538,0.0094,0.0011</t>
-  </si>
-  <si>
-    <t>0.2007,0.0268,0.9084,0.0012</t>
-  </si>
-  <si>
-    <t>0.1739,0.0253,0.8904,0.0003</t>
-  </si>
-  <si>
-    <t>0.9422,0.0052,0.0448,0.0010</t>
-  </si>
-  <si>
-    <t>0.9327,0.0004,0.0718,0.0007</t>
-  </si>
-  <si>
-    <t>0.0045,0.0062,0.9954,0.0002</t>
-  </si>
-  <si>
-    <t>0.4703,0.0135,0.7342,0.0010</t>
-  </si>
-  <si>
-    <t>0.9595,0.0018,0.0012,0.0179</t>
-  </si>
-  <si>
-    <t>0.9161,0.0021,0.0039,0.0631</t>
-  </si>
-  <si>
-    <t>0.9578,0.0029,0.0022,0.0262</t>
-  </si>
-  <si>
-    <t>0.5142,0.1014,0.3139,0.0820</t>
-  </si>
-  <si>
-    <t>0.9619,0.0025,0.0050,0.0153</t>
-  </si>
-  <si>
-    <t>0.9687,0.0026,0.0042,0.0052</t>
-  </si>
-  <si>
-    <t>0.9888,0.0005,0.0006,0.0047</t>
-  </si>
-  <si>
-    <t>0.0039,0.9250,0.9476,0.0005</t>
-  </si>
-  <si>
-    <t>0.6019,0.0267,0.5268,0.0005</t>
-  </si>
-  <si>
-    <t>0.0896,0.0074,0.9637,0.0003</t>
-  </si>
-  <si>
-    <t>0.0282,0.1625,0.9658,0.0003</t>
-  </si>
-  <si>
-    <t>0.0845,0.0023,0.9472,0.0007</t>
-  </si>
-  <si>
-    <t>0.9324,0.0399,0.0071,0.0003</t>
-  </si>
-  <si>
-    <t>0.1652,0.9286,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.9456,0.0054,0.0278,0.0028</t>
-  </si>
-  <si>
-    <t>0.9779,0.0009,0.0128,0.0005</t>
-  </si>
-  <si>
-    <t>0.0419,0.3063,0.8305,0.0021</t>
-  </si>
-  <si>
-    <t>0.3190,0.1270,0.7237,0.0011</t>
-  </si>
-  <si>
-    <t>0.2986,0.5523,0.1778,0.0006</t>
-  </si>
-  <si>
-    <t>0.0118,0.9838,0.1071,0.0002</t>
-  </si>
-  <si>
-    <t>0.0050,0.9305,0.9321,0.0010</t>
-  </si>
-  <si>
-    <t>0.9129,0.0012,0.0200,0.0226</t>
-  </si>
-  <si>
-    <t>0.9523,0.0001,0.0004,0.0783</t>
-  </si>
-  <si>
-    <t>0.9233,0.0001,0.0003,0.1347</t>
-  </si>
-  <si>
-    <t>0.8717,0.0007,0.0029,0.1673</t>
-  </si>
-  <si>
-    <t>0.9598,0.0002,0.0026,0.0171</t>
-  </si>
-  <si>
-    <t>0.9898,0.0001,0.0002,0.0089</t>
-  </si>
-  <si>
-    <t>0.0015,0.8806,0.9933,0.0002</t>
-  </si>
-  <si>
-    <t>0.0589,0.0759,0.9622,0.0004</t>
-  </si>
-  <si>
-    <t>0.1742,0.0237,0.8602,0.0007</t>
-  </si>
-  <si>
-    <t>0.0837,0.0565,0.9437,0.0010</t>
-  </si>
-  <si>
-    <t>0.6582,0.0898,0.1767,0.0008</t>
-  </si>
-  <si>
-    <t>0.0960,0.1687,0.9227,0.0003</t>
-  </si>
-  <si>
-    <t>0.9471,0.0032,0.0046,0.0273</t>
-  </si>
-  <si>
-    <t>0.9387,0.0029,0.0148,0.0134</t>
-  </si>
-  <si>
-    <t>0.9224,0.0035,0.0121,0.0300</t>
-  </si>
-  <si>
-    <t>0.8836,0.0058,0.0069,0.0629</t>
-  </si>
-  <si>
-    <t>0.9730,0.0007,0.0008,0.0221</t>
-  </si>
-  <si>
-    <t>0.9474,0.0049,0.0019,0.0277</t>
-  </si>
-  <si>
-    <t>0.9766,0.0001,0.0003,0.0305</t>
-  </si>
-  <si>
-    <t>0.9030,0.0081,0.0171,0.0345</t>
-  </si>
-  <si>
-    <t>0.9859,0.0004,0.0002,0.0072</t>
-  </si>
-  <si>
-    <t>0.9482,0.0010,0.0008,0.0544</t>
-  </si>
-  <si>
-    <t>0.9594,0.0038,0.0031,0.0150</t>
-  </si>
-  <si>
-    <t>0.9249,0.0002,0.0004,0.1394</t>
-  </si>
-  <si>
-    <t>0.8135,0.0019,0.0025,0.2417</t>
-  </si>
-  <si>
-    <t>0.9114,0.0011,0.0014,0.1328</t>
-  </si>
-  <si>
-    <t>0.8901,0.0029,0.0025,0.1204</t>
-  </si>
-  <si>
-    <t>0.9432,0.0023,0.0048,0.0511</t>
-  </si>
-  <si>
-    <t>0.0370,0.0013,0.9828,0.0008</t>
-  </si>
-  <si>
-    <t>0.8963,0.0026,0.1394,0.0013</t>
-  </si>
-  <si>
-    <t>0.9966,0.0001,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9368,0.0010,0.0490,0.0016</t>
-  </si>
-  <si>
-    <t>0.7975,0.1077,0.0351,0.0023</t>
-  </si>
-  <si>
-    <t>0.9877,0.0012,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.9842,0.0021,0.0025,0.0008</t>
-  </si>
-  <si>
-    <t>0.8959,0.0151,0.0400,0.0049</t>
-  </si>
-  <si>
-    <t>0.7883,0.1265,0.0122,0.0050</t>
-  </si>
-  <si>
-    <t>0.7484,0.2064,0.0409,0.0020</t>
-  </si>
-  <si>
-    <t>0.9203,0.0152,0.0175,0.0045</t>
-  </si>
-  <si>
-    <t>0.9901,0.0003,0.0035,0.0004</t>
-  </si>
-  <si>
-    <t>0.9565,0.0014,0.0340,0.0017</t>
-  </si>
-  <si>
-    <t>0.9497,0.0007,0.0125,0.0067</t>
-  </si>
-  <si>
-    <t>0.9291,0.0025,0.0774,0.0015</t>
-  </si>
-  <si>
-    <t>0.8479,0.0047,0.0553,0.0195</t>
-  </si>
-  <si>
-    <t>0.9552,0.0191,0.0050,0.0004</t>
-  </si>
-  <si>
-    <t>0.9393,0.0366,0.0062,0.0006</t>
-  </si>
-  <si>
-    <t>0.7613,0.0266,0.1594,0.0124</t>
-  </si>
-  <si>
-    <t>0.1304,0.7470,0.2625,0.0004</t>
-  </si>
-  <si>
-    <t>0.9543,0.0083,0.0138,0.0026</t>
-  </si>
-  <si>
-    <t>0.8866,0.0061,0.0741,0.0040</t>
-  </si>
-  <si>
-    <t>0.9603,0.0059,0.0189,0.0025</t>
-  </si>
-  <si>
-    <t>0.9585,0.0019,0.0068,0.0092</t>
-  </si>
-  <si>
-    <t>0.9868,0.0004,0.0003,0.0048</t>
-  </si>
-  <si>
-    <t>0.9230,0.0069,0.0064,0.0236</t>
-  </si>
-  <si>
-    <t>0.9562,0.0014,0.0035,0.0116</t>
-  </si>
-  <si>
-    <t>0.9629,0.0012,0.0028,0.0195</t>
-  </si>
-  <si>
-    <t>0.9647,0.0006,0.0026,0.0190</t>
-  </si>
-  <si>
-    <t>0.9183,0.0069,0.0078,0.0456</t>
-  </si>
-  <si>
-    <t>0.8640,0.0403,0.0237,0.0115</t>
-  </si>
-  <si>
-    <t>0.7755,0.0181,0.2590,0.0005</t>
-  </si>
-  <si>
-    <t>0.8582,0.0138,0.1589,0.0004</t>
-  </si>
-  <si>
-    <t>0.6383,0.0206,0.4775,0.0013</t>
-  </si>
-  <si>
-    <t>0.4611,0.0421,0.6218,0.0006</t>
-  </si>
-  <si>
-    <t>0.9957,0.0001,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9760,0.0007,0.0183,0.0006</t>
-  </si>
-  <si>
-    <t>0.9867,0.0004,0.0059,0.0005</t>
-  </si>
-  <si>
-    <t>0.9717,0.0013,0.0125,0.0014</t>
-  </si>
-  <si>
-    <t>0.9684,0.0003,0.0035,0.0106</t>
-  </si>
-  <si>
-    <t>0.3259,0.0006,0.0051,0.8160</t>
-  </si>
-  <si>
-    <t>0.3098,0.0005,0.0016,0.8798</t>
-  </si>
-  <si>
-    <t>0.8587,0.0000,0.0003,0.2656</t>
-  </si>
-  <si>
-    <t>0.0212,0.9754,0.0362,0.0002</t>
-  </si>
-  <si>
-    <t>0.9780,0.0002,0.0003,0.0126</t>
-  </si>
-  <si>
-    <t>0.9402,0.0113,0.0050,0.0086</t>
-  </si>
-  <si>
-    <t>0.9544,0.0030,0.0087,0.0108</t>
-  </si>
-  <si>
-    <t>0.8682,0.0371,0.0321,0.0186</t>
-  </si>
-  <si>
-    <t>0.9631,0.0021,0.0018,0.0144</t>
-  </si>
-  <si>
-    <t>0.9172,0.0006,0.0014,0.0877</t>
-  </si>
-  <si>
-    <t>0.9731,0.0032,0.0020,0.0054</t>
-  </si>
-  <si>
-    <t>0.1455,0.0940,0.9166,0.0161</t>
-  </si>
-  <si>
-    <t>0.8692,0.0008,0.0032,0.1562</t>
-  </si>
-  <si>
-    <t>0.9692,0.0004,0.0008,0.0289</t>
-  </si>
-  <si>
-    <t>0.9900,0.0009,0.0021,0.0004</t>
-  </si>
-  <si>
-    <t>0.9917,0.0002,0.0009,0.0013</t>
-  </si>
-  <si>
-    <t>0.9682,0.0015,0.0124,0.0023</t>
-  </si>
-  <si>
-    <t>0.9576,0.0027,0.0083,0.0039</t>
-  </si>
-  <si>
-    <t>0.9817,0.0011,0.0042,0.0008</t>
-  </si>
-  <si>
-    <t>0.9930,0.0003,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.9624,0.0004,0.0015,0.0208</t>
-  </si>
-  <si>
-    <t>0.9724,0.0010,0.0006,0.0208</t>
-  </si>
-  <si>
-    <t>0.9921,0.0005,0.0003,0.0024</t>
-  </si>
-  <si>
-    <t>0.9648,0.0013,0.0013,0.0232</t>
-  </si>
-  <si>
-    <t>0.8911,0.0115,0.0156,0.0507</t>
-  </si>
-  <si>
-    <t>0.8797,0.0112,0.0103,0.0428</t>
-  </si>
-  <si>
-    <t>0.9689,0.0025,0.0023,0.0081</t>
-  </si>
-  <si>
-    <t>0.9555,0.0005,0.0018,0.0313</t>
-  </si>
-  <si>
-    <t>0.9921,0.0005,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.9838,0.0010,0.0024,0.0007</t>
-  </si>
-  <si>
-    <t>0.9845,0.0010,0.0022,0.0016</t>
-  </si>
-  <si>
-    <t>0.8139,0.0173,0.1983,0.0134</t>
-  </si>
-  <si>
-    <t>0.9847,0.0006,0.0012,0.0038</t>
-  </si>
-  <si>
-    <t>0.9931,0.0003,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.9554,0.0090,0.0051,0.0042</t>
-  </si>
-  <si>
-    <t>0.9823,0.0011,0.0006,0.0034</t>
-  </si>
-  <si>
-    <t>0.0037,0.2932,0.9896,0.0007</t>
-  </si>
-  <si>
-    <t>0.9571,0.0025,0.0012,0.0175</t>
-  </si>
-  <si>
-    <t>0.0509,0.0451,0.9529,0.0003</t>
-  </si>
-  <si>
-    <t>0.6281,0.0090,0.6328,0.0003</t>
-  </si>
-  <si>
-    <t>0.9251,0.0044,0.0848,0.0011</t>
-  </si>
-  <si>
-    <t>0.2269,0.0171,0.8830,0.0003</t>
-  </si>
-  <si>
-    <t>0.2686,0.0122,0.8867,0.0005</t>
-  </si>
-  <si>
-    <t>0.0201,0.0105,0.9878,0.0003</t>
-  </si>
-  <si>
-    <t>0.1620,0.0240,0.8972,0.0022</t>
-  </si>
-  <si>
-    <t>0.9007,0.0019,0.1270,0.0011</t>
-  </si>
-  <si>
-    <t>0.5727,0.0111,0.5471,0.0026</t>
-  </si>
-  <si>
-    <t>0.9651,0.0008,0.0151,0.0021</t>
-  </si>
-  <si>
-    <t>0.9192,0.0036,0.1278,0.0005</t>
-  </si>
-  <si>
-    <t>0.9557,0.0032,0.0364,0.0008</t>
-  </si>
-  <si>
-    <t>0.9780,0.0005,0.0186,0.0005</t>
-  </si>
-  <si>
-    <t>0.9809,0.0008,0.0050,0.0015</t>
-  </si>
-  <si>
-    <t>0.9633,0.0012,0.0258,0.0006</t>
-  </si>
-  <si>
-    <t>0.9494,0.0088,0.0087,0.0094</t>
-  </si>
-  <si>
-    <t>0.9941,0.0006,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.8551,0.0515,0.0150,0.0058</t>
-  </si>
-  <si>
-    <t>0.9522,0.0020,0.0012,0.0308</t>
-  </si>
-  <si>
-    <t>0.9747,0.0032,0.0014,0.0052</t>
-  </si>
-  <si>
-    <t>0.9939,0.0002,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.7032,0.0017,0.3267,0.0035</t>
-  </si>
-  <si>
-    <t>0.9819,0.0001,0.0137,0.0002</t>
-  </si>
-  <si>
-    <t>0.9900,0.0002,0.0070,0.0001</t>
-  </si>
-  <si>
-    <t>0.9863,0.0001,0.0098,0.0003</t>
-  </si>
-  <si>
-    <t>0.6623,0.0075,0.4755,0.0022</t>
-  </si>
-  <si>
-    <t>0.8073,0.0048,0.2245,0.0026</t>
-  </si>
-  <si>
-    <t>0.2701,0.0217,0.8122,0.0029</t>
-  </si>
-  <si>
-    <t>0.4205,0.0148,0.7053,0.0017</t>
-  </si>
-  <si>
-    <t>0.0706,0.0398,0.9069,0.0006</t>
-  </si>
-  <si>
-    <t>0.9461,0.0009,0.0010,0.0427</t>
-  </si>
-  <si>
-    <t>0.7238,0.0172,0.0243,0.1874</t>
-  </si>
-  <si>
-    <t>0.9336,0.0004,0.0003,0.0770</t>
-  </si>
-  <si>
-    <t>0.9598,0.0052,0.0012,0.0059</t>
-  </si>
-  <si>
-    <t>0.8873,0.0092,0.0046,0.0421</t>
-  </si>
-  <si>
-    <t>0.9309,0.0053,0.0105,0.0324</t>
-  </si>
-  <si>
-    <t>0.9718,0.0011,0.0006,0.0128</t>
-  </si>
-  <si>
-    <t>0.9649,0.0006,0.0014,0.0203</t>
-  </si>
-  <si>
-    <t>0.2392,0.0202,0.8153,0.0076</t>
-  </si>
-  <si>
-    <t>0.8119,0.0193,0.1242,0.0192</t>
-  </si>
-  <si>
-    <t>0.9753,0.0004,0.0024,0.0094</t>
-  </si>
-  <si>
-    <t>0.1165,0.0336,0.9350,0.0004</t>
-  </si>
-  <si>
-    <t>0.0388,0.0749,0.9456,0.0014</t>
-  </si>
-  <si>
-    <t>0.8646,0.0058,0.1887,0.0008</t>
-  </si>
-  <si>
-    <t>0.0016,0.0043,0.9983,0.0002</t>
-  </si>
-  <si>
-    <t>0.6793,0.0270,0.4463,0.0021</t>
-  </si>
-  <si>
-    <t>0.0039,0.0066,0.9969,0.0002</t>
-  </si>
-  <si>
-    <t>0.0574,0.0246,0.9654,0.0005</t>
-  </si>
-  <si>
-    <t>0.8607,0.0092,0.1639,0.0012</t>
-  </si>
-  <si>
-    <t>0.9613,0.0009,0.0303,0.0007</t>
-  </si>
-  <si>
-    <t>0.9866,0.0003,0.0102,0.0002</t>
-  </si>
-  <si>
-    <t>0.9937,0.0001,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.9652,0.0005,0.0006,0.0382</t>
-  </si>
-  <si>
-    <t>0.9830,0.0013,0.0020,0.0035</t>
-  </si>
-  <si>
-    <t>0.9248,0.0074,0.0132,0.0208</t>
-  </si>
-  <si>
-    <t>0.9569,0.0060,0.0051,0.0080</t>
-  </si>
-  <si>
-    <t>0.9695,0.0002,0.0002,0.0480</t>
-  </si>
-  <si>
-    <t>0.9145,0.0054,0.0054,0.0523</t>
-  </si>
-  <si>
-    <t>0.9766,0.0008,0.0008,0.0144</t>
-  </si>
-  <si>
-    <t>0.9521,0.0002,0.0003,0.0799</t>
-  </si>
-  <si>
-    <t>0.9169,0.0054,0.1087,0.0005</t>
-  </si>
-  <si>
-    <t>0.7581,0.0128,0.3563,0.0005</t>
-  </si>
-  <si>
-    <t>0.4002,0.0072,0.7751,0.0009</t>
-  </si>
-  <si>
-    <t>0.7053,0.0704,0.2543,0.0019</t>
-  </si>
-  <si>
-    <t>0.0687,0.0015,0.9769,0.0001</t>
-  </si>
-  <si>
-    <t>0.9850,0.0004,0.0068,0.0003</t>
-  </si>
-  <si>
-    <t>0.9366,0.0023,0.0893,0.0010</t>
-  </si>
-  <si>
-    <t>0.2506,0.0052,0.8224,0.0018</t>
-  </si>
-  <si>
-    <t>0.9762,0.0000,0.0010,0.0067</t>
-  </si>
-  <si>
-    <t>0.9641,0.0004,0.0066,0.0064</t>
-  </si>
-  <si>
-    <t>0.9908,0.0000,0.0001,0.0076</t>
-  </si>
-  <si>
-    <t>0.9591,0.0002,0.0011,0.0270</t>
-  </si>
-  <si>
-    <t>0.5678,0.0000,0.0011,0.3578</t>
-  </si>
-  <si>
-    <t>0.9656,0.0007,0.0103,0.0041</t>
+    <t>0.9124,0.0154,0.0309,0.0328</t>
+  </si>
+  <si>
+    <t>0.0257,0.0020,0.0001,0.9911</t>
+  </si>
+  <si>
+    <t>0.7381,0.0136,0.0028,0.3165</t>
+  </si>
+  <si>
+    <t>0.8426,0.0048,0.0013,0.2416</t>
+  </si>
+  <si>
+    <t>0.9970,0.0010,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9924,0.0085,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9965,0.0008,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9927,0.0003,0.0003,0.0069</t>
+  </si>
+  <si>
+    <t>0.9917,0.0031,0.0011,0.0023</t>
+  </si>
+  <si>
+    <t>0.9954,0.0028,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9953,0.0014,0.0011,0.0008</t>
+  </si>
+  <si>
+    <t>0.9919,0.0018,0.0041,0.0007</t>
+  </si>
+  <si>
+    <t>0.9729,0.0021,0.0289,0.0003</t>
+  </si>
+  <si>
+    <t>0.4655,0.0064,0.7581,0.0036</t>
+  </si>
+  <si>
+    <t>0.7238,0.0207,0.3085,0.0007</t>
+  </si>
+  <si>
+    <t>0.0276,0.0161,0.9559,0.0006</t>
+  </si>
+  <si>
+    <t>0.7886,0.0029,0.3733,0.0014</t>
+  </si>
+  <si>
+    <t>0.0012,0.9975,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9991,0.0038,0.0006</t>
+  </si>
+  <si>
+    <t>0.0447,0.9631,0.0100,0.0008</t>
+  </si>
+  <si>
+    <t>0.0015,0.9954,0.0036,0.0014</t>
+  </si>
+  <si>
+    <t>0.0017,0.9966,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.9145,0.0101,0.0797,0.0043</t>
+  </si>
+  <si>
+    <t>0.4971,0.0086,0.6691,0.0013</t>
+  </si>
+  <si>
+    <t>0.0036,0.0005,0.9970,0.0001</t>
+  </si>
+  <si>
+    <t>0.0096,0.0013,0.9863,0.0017</t>
+  </si>
+  <si>
+    <t>0.0747,0.0008,0.9709,0.0004</t>
+  </si>
+  <si>
+    <t>0.0140,0.0007,0.9873,0.0003</t>
+  </si>
+  <si>
+    <t>0.0071,0.0003,0.9949,0.0005</t>
+  </si>
+  <si>
+    <t>0.2527,0.8059,0.0125,0.0037</t>
+  </si>
+  <si>
+    <t>0.6284,0.2929,0.0940,0.0038</t>
+  </si>
+  <si>
+    <t>0.0021,0.0125,0.9951,0.0020</t>
+  </si>
+  <si>
+    <t>0.0059,0.9291,0.1962,0.0006</t>
+  </si>
+  <si>
+    <t>0.9018,0.0757,0.0176,0.0118</t>
+  </si>
+  <si>
+    <t>0.8697,0.0169,0.0670,0.0331</t>
+  </si>
+  <si>
+    <t>0.5870,0.5303,0.0064,0.0022</t>
+  </si>
+  <si>
+    <t>0.0012,0.9962,0.0354,0.0004</t>
+  </si>
+  <si>
+    <t>0.0246,0.9009,0.1503,0.0098</t>
+  </si>
+  <si>
+    <t>0.0032,0.0083,0.9904,0.0036</t>
+  </si>
+  <si>
+    <t>0.6120,0.0090,0.4498,0.0032</t>
+  </si>
+  <si>
+    <t>0.0019,0.0007,0.9908,0.0072</t>
+  </si>
+  <si>
+    <t>0.0029,0.2736,0.9893,0.0008</t>
+  </si>
+  <si>
+    <t>0.0097,0.9433,0.0247,0.0002</t>
+  </si>
+  <si>
+    <t>0.0038,0.0036,0.9941,0.0007</t>
+  </si>
+  <si>
+    <t>0.0094,0.3916,0.0014,0.8996</t>
+  </si>
+  <si>
+    <t>0.0024,0.9795,0.0313,0.0192</t>
+  </si>
+  <si>
+    <t>0.0053,0.9920,0.0068,0.0007</t>
+  </si>
+  <si>
+    <t>0.0003,0.9988,0.0043,0.0003</t>
+  </si>
+  <si>
+    <t>0.0042,0.1056,0.9145,0.0036</t>
+  </si>
+  <si>
+    <t>0.0004,0.0227,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0101,0.0061,0.9766,0.0067</t>
+  </si>
+  <si>
+    <t>0.0066,0.0008,0.9916,0.0007</t>
+  </si>
+  <si>
+    <t>0.0067,0.0312,0.9885,0.0010</t>
+  </si>
+  <si>
+    <t>0.0034,0.0859,0.9732,0.0066</t>
+  </si>
+  <si>
+    <t>0.9837,0.0161,0.0010,0.0015</t>
+  </si>
+  <si>
+    <t>0.9954,0.0007,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.9938,0.0013,0.0019,0.0011</t>
+  </si>
+  <si>
+    <t>0.0070,0.0594,0.9876,0.0177</t>
+  </si>
+  <si>
+    <t>0.9884,0.0047,0.0057,0.0008</t>
+  </si>
+  <si>
+    <t>0.9834,0.0194,0.0023,0.0012</t>
+  </si>
+  <si>
+    <t>0.9886,0.0095,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.0013,0.9586,0.9707,0.0008</t>
+  </si>
+  <si>
+    <t>0.0040,0.0296,0.9918,0.0013</t>
+  </si>
+  <si>
+    <t>0.0006,0.0017,0.9981,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.9802,0.9906,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0004,0.9979,0.0006</t>
+  </si>
+  <si>
+    <t>0.0031,0.9944,0.0035,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.9975,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.8689,0.0031,0.1493,0.0039</t>
+  </si>
+  <si>
+    <t>0.9329,0.0026,0.1256,0.0008</t>
+  </si>
+  <si>
+    <t>0.0019,0.0036,0.9958,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.9935,0.9867,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9766,0.8329,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.9978,0.0875,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.9854,0.6747,0.0006</t>
+  </si>
+  <si>
+    <t>0.0107,0.0004,0.0257,0.9812</t>
+  </si>
+  <si>
+    <t>0.0014,0.0019,0.0009,0.9984</t>
+  </si>
+  <si>
+    <t>0.0021,0.0005,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.0149,0.0007,0.0002,0.9962</t>
+  </si>
+  <si>
+    <t>0.0038,0.0004,0.0003,0.9988</t>
+  </si>
+  <si>
+    <t>0.0051,0.0068,0.0041,0.9949</t>
+  </si>
+  <si>
+    <t>0.0000,0.9971,0.9878,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.4665,0.9911,0.0009</t>
+  </si>
+  <si>
+    <t>0.0067,0.7679,0.8182,0.0008</t>
+  </si>
+  <si>
+    <t>0.0008,0.8896,0.9364,0.0003</t>
+  </si>
+  <si>
+    <t>0.0013,0.9903,0.2838,0.0002</t>
+  </si>
+  <si>
+    <t>0.0023,0.9304,0.8876,0.0006</t>
+  </si>
+  <si>
+    <t>0.9963,0.0017,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9855,0.0121,0.0019,0.0019</t>
+  </si>
+  <si>
+    <t>0.9915,0.0073,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9852,0.0078,0.0025,0.0040</t>
+  </si>
+  <si>
+    <t>0.9965,0.0015,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9704,0.0289,0.0027,0.0039</t>
+  </si>
+  <si>
+    <t>0.9964,0.0015,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9942,0.0010,0.0012,0.0016</t>
+  </si>
+  <si>
+    <t>0.9952,0.0006,0.0005,0.0023</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9866,0.0066,0.0062,0.0015</t>
+  </si>
+  <si>
+    <t>0.9971,0.0006,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9923,0.0037,0.0015,0.0010</t>
+  </si>
+  <si>
+    <t>0.9933,0.0029,0.0007,0.0015</t>
+  </si>
+  <si>
+    <t>0.9950,0.0005,0.0005,0.0026</t>
+  </si>
+  <si>
+    <t>0.0077,0.0007,0.9948,0.0022</t>
+  </si>
+  <si>
+    <t>0.0635,0.0019,0.9689,0.0002</t>
+  </si>
+  <si>
+    <t>0.9331,0.0007,0.0351,0.0040</t>
+  </si>
+  <si>
+    <t>0.0237,0.0028,0.9687,0.0025</t>
+  </si>
+  <si>
+    <t>0.0023,0.9944,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.0026,0.9953,0.0031,0.0003</t>
+  </si>
+  <si>
+    <t>0.1550,0.8524,0.0124,0.0063</t>
+  </si>
+  <si>
+    <t>0.0444,0.9505,0.0109,0.0008</t>
+  </si>
+  <si>
+    <t>0.0005,0.9981,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.0013,0.9961,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.8000,0.2027,0.0144,0.0019</t>
+  </si>
+  <si>
+    <t>0.7648,0.0968,0.1483,0.0388</t>
+  </si>
+  <si>
+    <t>0.3643,0.0052,0.6954,0.0057</t>
+  </si>
+  <si>
+    <t>0.1701,0.0377,0.7746,0.0240</t>
+  </si>
+  <si>
+    <t>0.2892,0.6959,0.0593,0.0133</t>
+  </si>
+  <si>
+    <t>0.0846,0.0439,0.0561,0.8731</t>
+  </si>
+  <si>
+    <t>0.0019,0.9957,0.0032,0.0006</t>
+  </si>
+  <si>
+    <t>0.0073,0.9877,0.0105,0.0022</t>
+  </si>
+  <si>
+    <t>0.0014,0.9933,0.0027,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.9986,0.2220,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.9930,0.0029,0.0014</t>
+  </si>
+  <si>
+    <t>0.8025,0.2024,0.0174,0.0031</t>
+  </si>
+  <si>
+    <t>0.5855,0.5278,0.0149,0.0019</t>
+  </si>
+  <si>
+    <t>0.9918,0.0032,0.0010,0.0020</t>
+  </si>
+  <si>
+    <t>0.9950,0.0006,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.9689,0.0083,0.0174,0.0036</t>
+  </si>
+  <si>
+    <t>0.9875,0.0044,0.0045,0.0014</t>
+  </si>
+  <si>
+    <t>0.9975,0.0001,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9700,0.0303,0.0034,0.0008</t>
+  </si>
+  <si>
+    <t>0.9842,0.0031,0.0061,0.0019</t>
+  </si>
+  <si>
+    <t>0.9721,0.0108,0.0047,0.0082</t>
+  </si>
+  <si>
+    <t>0.0007,0.8102,0.9954,0.0007</t>
+  </si>
+  <si>
+    <t>0.0012,0.9149,0.9536,0.0005</t>
+  </si>
+  <si>
+    <t>0.0033,0.0156,0.9885,0.0018</t>
+  </si>
+  <si>
+    <t>0.0197,0.5670,0.7485,0.0008</t>
+  </si>
+  <si>
+    <t>0.9913,0.0011,0.0049,0.0002</t>
+  </si>
+  <si>
+    <t>0.1672,0.0094,0.8275,0.0218</t>
+  </si>
+  <si>
+    <t>0.0326,0.0013,0.9775,0.0062</t>
+  </si>
+  <si>
+    <t>0.4843,0.0158,0.6376,0.0063</t>
+  </si>
+  <si>
+    <t>0.0318,0.0020,0.0040,0.9806</t>
+  </si>
+  <si>
+    <t>0.0000,0.0027,0.0003,0.9997</t>
+  </si>
+  <si>
+    <t>0.0041,0.0054,0.0004,0.9971</t>
+  </si>
+  <si>
+    <t>0.0102,0.0004,0.0004,0.9970</t>
+  </si>
+  <si>
+    <t>0.0029,0.9725,0.0749,0.0007</t>
+  </si>
+  <si>
+    <t>0.9936,0.0016,0.0024,0.0003</t>
+  </si>
+  <si>
+    <t>0.0865,0.8841,0.0421,0.0345</t>
+  </si>
+  <si>
+    <t>0.9910,0.0013,0.0013,0.0031</t>
+  </si>
+  <si>
+    <t>0.4906,0.5380,0.0100,0.0032</t>
+  </si>
+  <si>
+    <t>0.9926,0.0012,0.0011,0.0021</t>
+  </si>
+  <si>
+    <t>0.3509,0.0044,0.0241,0.7082</t>
+  </si>
+  <si>
+    <t>0.9929,0.0011,0.0025,0.0016</t>
+  </si>
+  <si>
+    <t>0.0164,0.1811,0.9680,0.0251</t>
+  </si>
+  <si>
+    <t>0.7704,0.0018,0.0016,0.3323</t>
+  </si>
+  <si>
+    <t>0.9643,0.0112,0.0023,0.0112</t>
+  </si>
+  <si>
+    <t>0.6149,0.3227,0.0302,0.0083</t>
+  </si>
+  <si>
+    <t>0.9841,0.0025,0.0024,0.0050</t>
+  </si>
+  <si>
+    <t>0.9709,0.0077,0.0138,0.0013</t>
+  </si>
+  <si>
+    <t>0.0433,0.8874,0.0728,0.0031</t>
+  </si>
+  <si>
+    <t>0.7717,0.0124,0.2317,0.0038</t>
+  </si>
+  <si>
+    <t>0.9751,0.0058,0.0154,0.0010</t>
+  </si>
+  <si>
+    <t>0.9842,0.0058,0.0069,0.0019</t>
+  </si>
+  <si>
+    <t>0.9858,0.0024,0.0102,0.0014</t>
+  </si>
+  <si>
+    <t>0.9822,0.0024,0.0041,0.0075</t>
+  </si>
+  <si>
+    <t>0.9966,0.0003,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9369,0.0529,0.0034,0.0119</t>
+  </si>
+  <si>
+    <t>0.9685,0.0139,0.0153,0.0032</t>
+  </si>
+  <si>
+    <t>0.9941,0.0010,0.0010,0.0011</t>
+  </si>
+  <si>
+    <t>0.9930,0.0007,0.0004,0.0036</t>
+  </si>
+  <si>
+    <t>0.7153,0.2039,0.0008,0.0192</t>
+  </si>
+  <si>
+    <t>0.2810,0.7682,0.0132,0.0013</t>
+  </si>
+  <si>
+    <t>0.9151,0.0628,0.0157,0.0066</t>
+  </si>
+  <si>
+    <t>0.6609,0.1590,0.1816,0.0052</t>
+  </si>
+  <si>
+    <t>0.9960,0.0020,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9662,0.0345,0.0037,0.0021</t>
+  </si>
+  <si>
+    <t>0.9821,0.0116,0.0046,0.0016</t>
+  </si>
+  <si>
+    <t>0.9739,0.0280,0.0020,0.0018</t>
+  </si>
+  <si>
+    <t>0.0005,0.0101,0.9991,0.0009</t>
+  </si>
+  <si>
+    <t>0.9588,0.0166,0.0165,0.0020</t>
+  </si>
+  <si>
+    <t>0.0139,0.0278,0.9892,0.0014</t>
+  </si>
+  <si>
+    <t>0.0007,0.2167,0.9947,0.0025</t>
+  </si>
+  <si>
+    <t>0.0172,0.0067,0.9780,0.0048</t>
+  </si>
+  <si>
+    <t>0.0102,0.3900,0.9641,0.0017</t>
+  </si>
+  <si>
+    <t>0.0010,0.0035,0.9959,0.0019</t>
+  </si>
+  <si>
+    <t>0.0008,0.0008,0.9978,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.0010,0.9976,0.0006</t>
+  </si>
+  <si>
+    <t>0.1614,0.0301,0.8724,0.0096</t>
+  </si>
+  <si>
+    <t>0.0975,0.0103,0.9226,0.0038</t>
+  </si>
+  <si>
+    <t>0.5261,0.0097,0.6051,0.0063</t>
+  </si>
+  <si>
+    <t>0.1674,0.5932,0.1213,0.0012</t>
+  </si>
+  <si>
+    <t>0.2871,0.0303,0.7476,0.0021</t>
+  </si>
+  <si>
+    <t>0.9145,0.0087,0.1044,0.0012</t>
+  </si>
+  <si>
+    <t>0.1219,0.0335,0.7725,0.0468</t>
+  </si>
+  <si>
+    <t>0.6454,0.0158,0.2632,0.0341</t>
+  </si>
+  <si>
+    <t>0.1947,0.8559,0.0102,0.0012</t>
+  </si>
+  <si>
+    <t>0.3238,0.7787,0.0019,0.0024</t>
+  </si>
+  <si>
+    <t>0.4542,0.6966,0.0012,0.0017</t>
+  </si>
+  <si>
+    <t>0.9937,0.0036,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9814,0.0163,0.0013,0.0017</t>
+  </si>
+  <si>
+    <t>0.9319,0.0147,0.0397,0.0034</t>
+  </si>
+  <si>
+    <t>0.9751,0.0018,0.0111,0.0023</t>
+  </si>
+  <si>
+    <t>0.7386,0.0014,0.1113,0.0356</t>
+  </si>
+  <si>
+    <t>0.8172,0.0086,0.2430,0.0015</t>
+  </si>
+  <si>
+    <t>0.2784,0.0089,0.7987,0.0177</t>
+  </si>
+  <si>
+    <t>0.0178,0.0073,0.9804,0.0047</t>
+  </si>
+  <si>
+    <t>0.0456,0.0313,0.9111,0.0148</t>
+  </si>
+  <si>
+    <t>0.0131,0.4913,0.9476,0.0055</t>
+  </si>
+  <si>
+    <t>0.0815,0.0242,0.9293,0.0021</t>
+  </si>
+  <si>
+    <t>0.0011,0.0302,0.9899,0.0008</t>
+  </si>
+  <si>
+    <t>0.9903,0.0026,0.0008,0.0045</t>
+  </si>
+  <si>
+    <t>0.9940,0.0008,0.0010,0.0017</t>
+  </si>
+  <si>
+    <t>0.9764,0.0291,0.0016,0.0015</t>
+  </si>
+  <si>
+    <t>0.9915,0.0020,0.0059,0.0004</t>
+  </si>
+  <si>
+    <t>0.9461,0.0435,0.0058,0.0065</t>
+  </si>
+  <si>
+    <t>0.9937,0.0044,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9893,0.0060,0.0021,0.0015</t>
+  </si>
+  <si>
+    <t>0.9918,0.0015,0.0008,0.0027</t>
+  </si>
+  <si>
+    <t>0.0028,0.0313,0.9939,0.0044</t>
+  </si>
+  <si>
+    <t>0.0542,0.0711,0.8832,0.0120</t>
+  </si>
+  <si>
+    <t>0.8242,0.0421,0.1476,0.0148</t>
+  </si>
+  <si>
+    <t>0.0014,0.0115,0.9980,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.0026,0.9959,0.0011</t>
+  </si>
+  <si>
+    <t>0.0237,0.1191,0.9342,0.0021</t>
+  </si>
+  <si>
+    <t>0.0034,0.0028,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0065,0.0030,0.9836,0.0001</t>
+  </si>
+  <si>
+    <t>0.0074,0.0224,0.9889,0.0011</t>
+  </si>
+  <si>
+    <t>0.0027,0.0026,0.9935,0.0016</t>
+  </si>
+  <si>
+    <t>0.0051,0.0115,0.9726,0.0048</t>
+  </si>
+  <si>
+    <t>0.9794,0.0004,0.0219,0.0005</t>
+  </si>
+  <si>
+    <t>0.8613,0.0134,0.1647,0.0109</t>
+  </si>
+  <si>
+    <t>0.9937,0.0003,0.0027,0.0002</t>
+  </si>
+  <si>
+    <t>0.9643,0.0671,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.9860,0.0208,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9955,0.0024,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9868,0.0063,0.0042,0.0016</t>
+  </si>
+  <si>
+    <t>0.9925,0.0042,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9929,0.0056,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9940,0.0038,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9940,0.0038,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.0073,0.0544,0.9745,0.0003</t>
+  </si>
+  <si>
+    <t>0.0057,0.4413,0.9703,0.0022</t>
+  </si>
+  <si>
+    <t>0.0127,0.0166,0.9670,0.0042</t>
+  </si>
+  <si>
+    <t>0.0556,0.2137,0.7162,0.0153</t>
+  </si>
+  <si>
+    <t>0.0014,0.0016,0.9961,0.0006</t>
+  </si>
+  <si>
+    <t>0.0190,0.0008,0.8420,0.1264</t>
+  </si>
+  <si>
+    <t>0.5184,0.0188,0.5579,0.0040</t>
+  </si>
+  <si>
+    <t>0.0102,0.0013,0.6414,0.2865</t>
+  </si>
+  <si>
+    <t>0.5853,0.0096,0.0138,0.4978</t>
+  </si>
+  <si>
+    <t>0.0100,0.0133,0.0011,0.9930</t>
+  </si>
+  <si>
+    <t>0.0624,0.0011,0.0002,0.9833</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0057,0.0043,0.0005,0.9963</t>
+  </si>
+  <si>
+    <t>0.9043,0.0029,0.0030,0.0979</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3521,7 +3521,7 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D114" t="s">
         <v>376</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3577,7 +3577,7 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
         <v>380</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3703,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3899,7 +3899,7 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
         <v>403</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3927,7 +3927,7 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
         <v>405</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4669,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
         <v>458</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4725,7 +4725,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
         <v>462</v>
@@ -4823,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
         <v>469</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
